--- a/worklog/v2.2.3/s10/v4/pjm/test/ods_material_info_v2.xlsx
+++ b/worklog/v2.2.3/s10/v4/pjm/test/ods_material_info_v2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="重要物料信息表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ods_material_info_v2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,282 +415,263 @@
   </sheetPr>
   <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="32" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
-    <col width="29" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="22" customWidth="1" min="29" max="29"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>项目编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>分系统/分任务</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>PBS编号</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PBS名称</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>自研或外协</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>供应商名称</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>是否长周期物料</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>合同完成谈判时间</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>合同完成谈判周数</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>合同要求到货时间</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>合同要求到货周数</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>实际到货时间</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>实际到货周数</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>计划检验时间</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>计划检验周数</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>完成检验时间</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>完成检验周数</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>上装时间</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>上装周数</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>责任科室/责任人</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>管控责任部门/责任人</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>本周进展</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>当前进展是否影响重要及以上节点</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>风险等级</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>主要风险内容及措施</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>延期影响分析</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新时间</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新周数</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>project_no</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>subsystem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pbs_no</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pbs_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>self_or_outsource</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>supplier_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_long_cycle</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>contract_negotiation_date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>contract_negotiation_week</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>contract_delivery_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>contract_delivery_week</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>actual_delivery_date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>actual_delivery_week</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>plan_inspect_date</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>plan_inspect_week</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>complete_inspect_date</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>complete_inspect_week</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>install_date</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>install_week</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>dept_owner</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>control_dept_owner</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>weekly_progress</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>affects_major_node</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>risk_level</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>risk_content</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>delay_impact</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>last_update_time</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>last_update_week</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>remark</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>控制分系统</t>
+          <t>总体分系统</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PBS-A01-001</t>
+          <t>PBS-C01-001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>主控芯片</t>
+          <t>综合控制机机箱</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>外协</t>
+          <t>自研</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>华大电子</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>19</v>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>18</v>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>19</v>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>19</v>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>20</v>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>陈工/控制室</t>
+          <t>王工/总体室</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>赵总/控制室</t>
+          <t>张总/总体室</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>芯片已到货并完成检验</t>
+          <t>已完成到货检验并进入装配</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -715,34 +684,39 @@
           <t>低</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>20</v>
-      </c>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>结构分系统</t>
+          <t>控制分系统</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PBS-A01-002</t>
+          <t>PBS-C02-001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>主承力结构件</t>
+          <t>飞控控制器样机</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -752,7 +726,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>江南机械</t>
+          <t>中航智控</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -762,65 +736,77 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>12</v>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>29</v>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>29</v>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>29</v>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>30</v>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>32</v>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>周工/结构室</t>
+          <t>陈工/控制室</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>吴总/结构室</t>
+          <t>赵总/控制室</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>结构件已上装</t>
+          <t>已完成到货检验并进入装配</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -833,19 +819,24 @@
           <t>低</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>32</v>
-      </c>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,12 +846,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PBS-A02-001</t>
+          <t>PBS-C03-001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>发动机喷管</t>
+          <t>动力控制组件</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -880,55 +871,43 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>15</v>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>29</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>30</v>
-      </c>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>30</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>32</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>33</v>
-      </c>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>钱工/动力室</t>
+          <t>赵工/动力室</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -938,258 +917,334 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>喷管已到货并完成检验</t>
+          <t>供应商正在加急排产，尚未到货</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>动力控制组件到货节奏存在波动</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>影响关键节点交付</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>33</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>与风险台账联动</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>动力分系统</t>
+          <t>制导分系统</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PBS-A02-002</t>
+          <t>PBS-C04-001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>发动机控制器</t>
+          <t>制导计算机板卡</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>自研</t>
+          <t>外协</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>中电十三所</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>林工/制导室</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>马总/制导室</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>已完成到货检验并进入装配</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>36</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>38</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>38</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>40</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>42</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>赵工/动力室</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>孙总/动力室</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>控制器单机完成</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>42</v>
-      </c>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>制导分系统</t>
+          <t>软件分系统</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PBS-B01-001</t>
+          <t>PBS-C05-001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>制导板卡元器件</t>
+          <t>实时软件构件包</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>外协</t>
+          <t>自研</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>中电十三所</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>10</v>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>30</v>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>黄工/制导室</t>
+          <t>沈工/软件室</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>马总/制导室</t>
+          <t>胡总/软件室</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>批次失效需更换</t>
+          <t>已完成到货检验并进入装配</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>批次元器件失效</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>影响制导初样硬件调试节点4周</t>
-        </is>
-      </c>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>39</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>与元器件失效风险联动</t>
-        </is>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>遥测分系统</t>
+          <t>结构分系统</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PBS-B02-001</t>
+          <t>PBS-C06-001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>遥测天线组件</t>
+          <t>主承力舱段结构件</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1199,7 +1254,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>航天五院</t>
+          <t>江南机械</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1209,90 +1264,95 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>15</v>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>30</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>30</v>
-      </c>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>31</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>33</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>34</v>
-      </c>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>徐工/电子室</t>
+          <t>周工/结构室</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>郑总/电子室</t>
+          <t>吴总/结构室</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>天线已到货并通过方向图测试</t>
+          <t>供应商正在加急排产，尚未到货</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>主承力舱段结构件到货节奏存在波动</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>影响关键节点交付</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>34</v>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>与风险台账联动</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XM-2026-B03</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1302,76 +1362,88 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PBS-B03-001</t>
+          <t>PBS-C07-001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>蓄电池组</t>
+          <t>电源管理单元</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>外协</t>
+          <t>自研</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>力神电池</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>13</v>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>25</v>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>25</v>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>26</v>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>28</v>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>30</v>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,7 +1457,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>蓄电池组已到货并完成循环测试</t>
+          <t>已完成到货检验并进入装配</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1398,34 +1470,39 @@
           <t>低</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>30</v>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XM-2026-B04</t>
+          <t>XM-2026-C08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>结构分系统</t>
+          <t>电子分系统</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PBS-B04-001</t>
+          <t>PBS-C08-001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>主承力结构件</t>
+          <t>载荷处理模块</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1435,7 +1512,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>沈阳黎明</t>
+          <t>航电电子</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1445,76 +1522,95 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>16</v>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>30</v>
-      </c>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>33</v>
-      </c>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>余工/结构室</t>
+          <t>徐工/电子室</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>吴总/结构室</t>
+          <t>郑总/电子室</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>结构件试制中</t>
+          <t>供应商正在加急排产，尚未到货</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>试制工艺尚未全线打通</t>
+          <t>载荷处理模块到货节奏存在波动</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>有1周影响风险</t>
+          <t>影响关键节点交付</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>39</v>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>与风险台账联动</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XM-2026-B05</t>
+          <t>XM-2026-C09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,76 +1620,88 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PBS-B05-001</t>
+          <t>PBS-C09-001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>测控主机元器件</t>
+          <t>测控主机样机</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>外协</t>
+          <t>自研</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>中电四十三所</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>14</v>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>25</v>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>25</v>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>26</v>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>28</v>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>30</v>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1607,7 +1715,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>元器件批次替换到位</t>
+          <t>已完成到货检验并进入装配</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1620,91 +1728,92 @@
           <t>低</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>30</v>
-      </c>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XM-2026-B06</t>
+          <t>XM-2026-C10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>综合试验分系统</t>
+          <t>试验分系统</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PBS-B06-001</t>
+          <t>PBS-C10-001</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>综合试验件</t>
+          <t>综合试验工装</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>自研</t>
+          <t>外协</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>航试装备</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>37</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>38</v>
-      </c>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>38</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>40</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>42</v>
-      </c>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>柳工/试验室</t>
@@ -1717,7 +1826,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>综合试验件完成组装</t>
+          <t>供应商正在加急排产，尚未到货</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1732,21 +1841,28 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>EMC与可靠性试验超标</t>
+          <t>综合试验工装到货节奏存在波动</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>鉴定试验延期风险</t>
+          <t>影响关键节点交付</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>51</v>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>与风险台账联动</t>
+        </is>
       </c>
     </row>
   </sheetData>
